--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$27</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -332,6 +335,9 @@
     <t>frenchDepartment</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/french-department}
 </t>
   </si>
@@ -347,9 +353,6 @@
   </si>
   <si>
     <t>Address.use</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -782,6 +785,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1097,7 +1115,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1199,7 +1217,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>79</v>
       </c>
@@ -1299,7 +1317,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>85</v>
       </c>
@@ -1401,7 +1419,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -1505,7 +1523,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>101</v>
       </c>
@@ -1526,7 +1544,7 @@
         <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>71</v>
@@ -1535,7 +1553,7 @@
         <v>71</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>99</v>
@@ -1607,15 +1625,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>85</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>71</v>
@@ -1628,7 +1646,7 @@
         <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>71</v>
@@ -1637,7 +1655,7 @@
         <v>71</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>99</v>
@@ -1709,12 +1727,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1731,10 +1749,10 @@
         <v>71</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>109</v>
@@ -1798,7 +1816,7 @@
         <v>71</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>72</v>
@@ -1813,7 +1831,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>119</v>
       </c>
@@ -1838,7 +1856,7 @@
         <v>71</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>109</v>
@@ -1915,7 +1933,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>126</v>
       </c>
@@ -1940,7 +1958,7 @@
         <v>71</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>81</v>
@@ -2019,7 +2037,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>132</v>
       </c>
@@ -2044,7 +2062,7 @@
         <v>71</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>81</v>
@@ -2121,7 +2139,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>137</v>
       </c>
@@ -2221,7 +2239,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>138</v>
       </c>
@@ -2323,7 +2341,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>139</v>
       </c>
@@ -2425,7 +2443,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>143</v>
       </c>
@@ -2527,7 +2545,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>147</v>
       </c>
@@ -2629,7 +2647,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>151</v>
       </c>
@@ -2731,7 +2749,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>155</v>
       </c>
@@ -2833,7 +2851,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>159</v>
       </c>
@@ -2935,7 +2953,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>164</v>
       </c>
@@ -3037,7 +3055,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>168</v>
       </c>
@@ -3137,7 +3155,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>172</v>
       </c>
@@ -3162,7 +3180,7 @@
         <v>71</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>81</v>
@@ -3239,7 +3257,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>177</v>
       </c>
@@ -3264,7 +3282,7 @@
         <v>71</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>81</v>
@@ -3341,7 +3359,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>183</v>
       </c>
@@ -3366,7 +3384,7 @@
         <v>71</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>81</v>
@@ -3443,7 +3461,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>187</v>
       </c>
@@ -3468,7 +3486,7 @@
         <v>71</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>81</v>
@@ -3545,7 +3563,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>192</v>
       </c>
@@ -3570,7 +3588,7 @@
         <v>71</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>81</v>
@@ -3647,7 +3665,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>196</v>
       </c>
@@ -3672,7 +3690,7 @@
         <v>71</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>197</v>
@@ -3752,6 +3770,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ27">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI26">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$25</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,30 +329,10 @@
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
-    <t>Address.extension:frenchDepartment</t>
-  </si>
-  <si>
-    <t>frenchDepartment</t>
+    <t>Address.use</t>
   </si>
   <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/french-department}
-</t>
-  </si>
-  <si>
-    <t>Address.extension:countryCode</t>
-  </si>
-  <si>
-    <t>countryCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/address-country-code}
-</t>
-  </si>
-  <si>
-    <t>Address.use</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -588,6 +568,9 @@
     <t>Madison</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J84-DepartementOM-RASS/FHIR/JDV-J84-DepartementOM-RASS</t>
+  </si>
+  <si>
     <t>Address.state</t>
   </si>
   <si>
@@ -627,6 +610,9 @@
   </si>
   <si>
     <t>ISO 3166 3 letter codes can be used in place of a full country name. FRA for France.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J74-Pays-RASS/FHIR/JDV-J74-Pays-RASS</t>
   </si>
   <si>
     <t>Address.period</t>
@@ -965,7 +951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.3984375" customWidth="true" bestFit="true"/>
@@ -978,7 +964,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.2890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -993,7 +979,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="39.6640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.23046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="92.66015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1528,11 +1514,9 @@
         <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>102</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>71</v>
       </c>
@@ -1544,25 +1528,29 @@
         <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="I6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="N6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O6" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P6" t="s" s="2">
         <v>71</v>
       </c>
@@ -1574,7 +1562,7 @@
         <v>71</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>71</v>
@@ -1586,13 +1574,13 @@
         <v>71</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>71</v>
@@ -1610,31 +1598,29 @@
         <v>71</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>71</v>
       </c>
@@ -1646,24 +1632,26 @@
         <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="I7" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="L7" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N7" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>71</v>
@@ -1676,7 +1664,7 @@
         <v>71</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="U7" t="s" s="2">
         <v>71</v>
@@ -1688,13 +1676,13 @@
         <v>71</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>71</v>
@@ -1712,27 +1700,27 @@
         <v>71</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1749,25 +1737,25 @@
         <v>71</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O8" t="s" s="2">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>71</v>
@@ -1780,7 +1768,7 @@
         <v>71</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="U8" t="s" s="2">
         <v>71</v>
@@ -1792,13 +1780,13 @@
         <v>71</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>71</v>
@@ -1816,7 +1804,7 @@
         <v>71</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>72</v>
@@ -1828,15 +1816,15 @@
         <v>78</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1847,7 +1835,7 @@
         <v>72</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>71</v>
@@ -1856,19 +1844,19 @@
         <v>71</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1882,7 +1870,7 @@
         <v>71</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="U9" t="s" s="2">
         <v>71</v>
@@ -1894,13 +1882,13 @@
         <v>71</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>71</v>
@@ -1918,27 +1906,27 @@
         <v>71</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1958,23 +1946,19 @@
         <v>71</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>71</v>
       </c>
@@ -1986,7 +1970,7 @@
         <v>71</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="U10" t="s" s="2">
         <v>71</v>
@@ -2022,7 +2006,7 @@
         <v>71</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>72</v>
@@ -2031,10 +2015,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>118</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -2046,7 +2030,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2062,19 +2046,19 @@
         <v>71</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2088,7 +2072,7 @@
         <v>71</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="U11" t="s" s="2">
         <v>71</v>
@@ -2112,19 +2096,19 @@
         <v>71</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>72</v>
@@ -2136,17 +2120,19 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>71</v>
       </c>
@@ -2155,7 +2141,7 @@
         <v>72</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>71</v>
@@ -2167,13 +2153,13 @@
         <v>71</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2224,31 +2210,33 @@
         <v>71</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>71</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2267,17 +2255,15 @@
         <v>71</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>90</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>71</v>
@@ -2314,16 +2300,16 @@
         <v>71</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>94</v>
@@ -2343,13 +2329,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>71</v>
@@ -2371,13 +2357,13 @@
         <v>71</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2445,13 +2431,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>71</v>
@@ -2473,13 +2459,13 @@
         <v>71</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2547,13 +2533,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>71</v>
@@ -2575,13 +2561,13 @@
         <v>71</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2649,13 +2635,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>71</v>
@@ -2677,13 +2663,13 @@
         <v>71</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2751,13 +2737,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>71</v>
@@ -2779,13 +2765,13 @@
         <v>71</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2853,14 +2839,12 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>71</v>
       </c>
@@ -2869,7 +2853,7 @@
         <v>72</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>71</v>
@@ -2881,10 +2865,10 @@
         <v>71</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
         <v>163</v>
@@ -2911,7 +2895,7 @@
         <v>71</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="X19" t="s" s="2">
         <v>71</v>
@@ -2938,40 +2922,38 @@
         <v>71</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>71</v>
@@ -2980,18 +2962,20 @@
         <v>71</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>71</v>
@@ -3004,7 +2988,7 @@
         <v>71</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>71</v>
@@ -3040,31 +3024,31 @@
         <v>71</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3074,24 +3058,26 @@
         <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>71</v>
@@ -3104,7 +3090,7 @@
         <v>71</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>71</v>
@@ -3113,16 +3099,14 @@
         <v>71</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>71</v>
@@ -3149,22 +3133,22 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3180,19 +3164,19 @@
         <v>71</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3206,7 +3190,7 @@
         <v>71</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>71</v>
@@ -3242,7 +3226,7 @@
         <v>71</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>72</v>
@@ -3254,19 +3238,19 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3282,19 +3266,19 @@
         <v>71</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3308,43 +3292,43 @@
         <v>71</v>
       </c>
       <c r="T23" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>72</v>
@@ -3356,19 +3340,19 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3378,25 +3362,25 @@
         <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3422,13 +3406,11 @@
         <v>71</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>71</v>
@@ -3446,7 +3428,7 @@
         <v>71</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
@@ -3458,19 +3440,19 @@
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3486,21 +3468,23 @@
         <v>71</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
       </c>
@@ -3512,7 +3496,7 @@
         <v>71</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>71</v>
@@ -3548,7 +3532,7 @@
         <v>71</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>72</v>
@@ -3560,217 +3544,11 @@
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="M27" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q27" s="2"/>
-      <c r="R27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>203</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ27">
+  <autoFilter ref="A1:AJ25">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3780,7 +3558,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI26">
+  <conditionalFormatting sqref="A2:AI24">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-address-extended.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>As Address Extended Profile</t>
+    <t>As Address Extended Profile (datatype)</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension créée dans le contexte de l'Annuaire Santé pour prise en compte des spécificités de l'adresse postale française</t>
+    <t>Datatype profile créé dans le contexte de l'Annuaire Santé pour prise en compte des spécificités de l'adresse postale française</t>
   </si>
   <si>
     <t>Purpose</t>
